--- a/python/Analysis/dsets.xlsx
+++ b/python/Analysis/dsets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adrian.negrean\Documents\AIND\SCBC project\Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adrian.negrean\Documents\GitHub\ophys-slap2-analysis\python\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2D2478-2E92-43EC-98AA-0019216185EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22339826-E562-4756-9B8C-A20C685EA1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24255" yWindow="1680" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24225" yWindow="3720" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>folder</t>
   </si>
@@ -88,6 +88,18 @@
   </si>
   <si>
     <t>use ROI 9 as example</t>
+  </si>
+  <si>
+    <t>ROI 1 has missing data from start of sweep and bleach fit fails badly</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>exclude ROI</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -138,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -148,6 +160,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -430,16 +448,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="2"/>
     <col min="3" max="3" width="54.140625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="4" max="4" width="9.140625" style="2"/>
+    <col min="5" max="5" width="16.140625" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -452,11 +472,14 @@
       <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -469,8 +492,14 @@
       <c r="D2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -484,7 +513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -498,7 +527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -511,11 +540,11 @@
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -529,7 +558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -542,8 +571,14 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -556,8 +591,11 @@
       <c r="D8" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -571,7 +609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
